--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-servicerequest-common.xlsx
@@ -389,7 +389,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.meta.versionId</t>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-servicerequest-common.xlsx
@@ -449,7 +449,7 @@
     <t>ServiceRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -545,7 +545,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
     <t>要求されたサービスの分類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>RF1-5</t>
@@ -952,7 +952,7 @@
     <t>指定された個人、組織、または医療サービスによって実施できるテストやサービスのコード。ラボの場合、LOINCが（preferred）[http://build.fhir.org/terminologies.html#preferred]であり、LOINCオーダーコードを使用した値セットが[こちら]（valueset-diagnostic-requests.html）で利用可能です。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -989,7 +989,7 @@
     <t>注文コンテキストに基づくコード化された注文詳細。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1129,7 +1129,7 @@
     <t>手続きを実行する前に満たされる必要がある前提条件を示すコード化された概念。たとえば、「痛み」、「フレアアップ時」など。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1224,7 +1224,7 @@
     <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1317,7 +1317,7 @@
     <t>サービス調査の依頼理由を正当化する診断または問題コード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1386,7 +1386,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1452,7 +1452,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1498,7 +1498,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1836,15 +1836,15 @@
   <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.71484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.71484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.62109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1855,27 +1855,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="194.140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="166.44140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="85.41796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="163.4453125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="66.88671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="73.23046875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="140.125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="57.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2699,7 +2699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -7839,12 +7839,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO51">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-servicerequest-common.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
